--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_50.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_50.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>InformationLevel</t>
+          <t>Attempt</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RiskTaking</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.4713063647962676</v>
+        <v>1.021285988225195</v>
       </c>
       <c r="C2">
-        <v>1.292357961014095</v>
+        <v>-0.8703500024691342</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3924564590794249</v>
+        <v>0.002274725576359003</v>
       </c>
       <c r="C3">
-        <v>-0.6354127755997407</v>
+        <v>0.4664683077172737</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.4972326596746174</v>
+        <v>-1.262387366615453</v>
       </c>
       <c r="C4">
-        <v>0.6802459797034719</v>
+        <v>-0.9724172246631745</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.02116352067548503</v>
+        <v>1.017038097895916</v>
       </c>
       <c r="C5">
-        <v>0.8043900087119286</v>
+        <v>0.1319742256880649</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.2003203803213589</v>
+        <v>-0.3609295722000614</v>
       </c>
       <c r="C6">
-        <v>-2.122005239407529</v>
+        <v>-0.06567998068326189</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.8899627328710593</v>
+        <v>0.6977403056405335</v>
       </c>
       <c r="C7">
-        <v>-0.1135384636907193</v>
+        <v>0.794470676957888</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.133023949789705</v>
+        <v>2.34293435793708</v>
       </c>
       <c r="C8">
-        <v>0.476174128215743</v>
+        <v>-0.1326937491122064</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.912716604476171</v>
+        <v>0.3968018194993626</v>
       </c>
       <c r="C9">
-        <v>0.06175166256249204</v>
+        <v>1.632090128133748</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.161636541373302</v>
+        <v>0.9028004203840644</v>
       </c>
       <c r="C10">
-        <v>-0.5454441074927825</v>
+        <v>-0.566879003127357</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.891090229650372</v>
+        <v>1.768167506372269</v>
       </c>
       <c r="C11">
-        <v>-1.961346489074508</v>
+        <v>-0.9103334809133994</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.770355051057095</v>
+        <v>-1.462813546848431</v>
       </c>
       <c r="C12">
-        <v>-0.2415798087076252</v>
+        <v>-1.137922905583343</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.7421455127219845</v>
+        <v>-0.4166575483840179</v>
       </c>
       <c r="C13">
-        <v>-0.1893628499151706</v>
+        <v>-0.4653270891843085</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-2.489786840339353</v>
+        <v>0.4558766469120599</v>
       </c>
       <c r="C14">
-        <v>1.387961066042497</v>
+        <v>-0.1106443014166823</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.5469634452565518</v>
+        <v>1.327526959197682</v>
       </c>
       <c r="C15">
-        <v>-0.7152713781668854</v>
+        <v>-0.1867220793598432</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.2782326476257304</v>
+        <v>0.08803326866568466</v>
       </c>
       <c r="C16">
-        <v>-0.9851828296875556</v>
+        <v>0.7209553139194804</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.6961281503727074</v>
+        <v>1.046181284603996</v>
       </c>
       <c r="C17">
-        <v>0.04115361046948973</v>
+        <v>-0.4317317346834061</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-1.026008762159898</v>
+        <v>-0.3036631303246603</v>
       </c>
       <c r="C18">
-        <v>0.2208927402938521</v>
+        <v>0.5811032492929499</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.8920767843586044</v>
+        <v>1.849074367013958</v>
       </c>
       <c r="C19">
-        <v>0.1524881279298841</v>
+        <v>0.7241742156247095</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.351876120993706</v>
+        <v>-0.4240924878269314</v>
       </c>
       <c r="C20">
-        <v>0.4999241765578399</v>
+        <v>-0.01920474143857318</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>2.070186262489299</v>
+        <v>-0.4710399366560762</v>
       </c>
       <c r="C21">
-        <v>-1.993462556566512</v>
+        <v>1.077525629644488</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.7188582489366042</v>
+        <v>0.3135115062064243</v>
       </c>
       <c r="C22">
-        <v>-0.7480583003968355</v>
+        <v>-0.3763303522409735</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.334950573515703</v>
+        <v>0.6128190493262832</v>
       </c>
       <c r="C23">
-        <v>1.387391002179088</v>
+        <v>-0.1378019601603062</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.6280780228904204</v>
+        <v>0.2243307675647941</v>
       </c>
       <c r="C24">
-        <v>-0.2580517001969761</v>
+        <v>-1.29012684265772</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.3064395591127484</v>
+        <v>-1.016298698833675</v>
       </c>
       <c r="C25">
-        <v>0.7910878060514661</v>
+        <v>-0.6818647368424871</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.511428407923878</v>
+        <v>-1.078297112969116</v>
       </c>
       <c r="C26">
-        <v>-1.488488910856034</v>
+        <v>-0.834348270196137</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.4529419851932162</v>
+        <v>-0.5970777469555888</v>
       </c>
       <c r="C27">
-        <v>0.6241011357999801</v>
+        <v>0.4673355865943924</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.5216389033264673</v>
+        <v>-1.338379796802249</v>
       </c>
       <c r="C28">
-        <v>0.836039572073862</v>
+        <v>1.081442912908646</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.82168539931555</v>
+        <v>0.5050310998515127</v>
       </c>
       <c r="C29">
-        <v>-0.4812152528963841</v>
+        <v>-0.3472124720224781</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.6525491586614383</v>
+        <v>-1.120671126086123</v>
       </c>
       <c r="C30">
-        <v>0.4104958713426785</v>
+        <v>-1.854977801036731</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.2638577303249555</v>
+        <v>1.158700648092282</v>
       </c>
       <c r="C31">
-        <v>-0.3921073675188335</v>
+        <v>0.6208340687400073</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.413459074067918</v>
+        <v>0.8002758741782851</v>
       </c>
       <c r="C32">
-        <v>-1.57826719244637</v>
+        <v>-0.1973286796656447</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>2.023409112866852</v>
+        <v>0.8934876381798259</v>
       </c>
       <c r="C33">
-        <v>-0.9704998731503189</v>
+        <v>0.4215911001682254</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.3687456420571348</v>
+        <v>-0.9083989000453652</v>
       </c>
       <c r="C34">
-        <v>-0.3402866138579745</v>
+        <v>-0.3485447688941998</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.538137454055092</v>
+        <v>-0.6425818821191885</v>
       </c>
       <c r="C35">
-        <v>1.547971049056331</v>
+        <v>-2.164153667620166</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.2021598308915304</v>
+        <v>1.394731079360766</v>
       </c>
       <c r="C36">
-        <v>-2.808318856069758</v>
+        <v>0.3938539415315735</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.8529592580872384</v>
+        <v>-0.4285002352784401</v>
       </c>
       <c r="C37">
-        <v>-1.299057056645456</v>
+        <v>-1.654428351735793</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.4365500768169125</v>
+        <v>0.3956893711996552</v>
       </c>
       <c r="C38">
-        <v>0.588332921837628</v>
+        <v>-3.004002785341128</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.1897651189578165</v>
+        <v>-0.2742129500563699</v>
       </c>
       <c r="C39">
-        <v>-0.4158615612609461</v>
+        <v>-0.570233103253897</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.3568071575974204</v>
+        <v>1.389512839698387</v>
       </c>
       <c r="C40">
-        <v>-1.654820868209818</v>
+        <v>0.7012065589175429</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>2.526335071939967</v>
+        <v>0.8521542841774045</v>
       </c>
       <c r="C41">
-        <v>-1.415083524778343</v>
+        <v>1.52516412361505</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.479111679452195</v>
+        <v>1.196411784519145</v>
       </c>
       <c r="C42">
-        <v>0.2798211138941903</v>
+        <v>0.5378350231812208</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-2.159274990221339</v>
+        <v>0.8963493807089092</v>
       </c>
       <c r="C43">
-        <v>0.07193811258255389</v>
+        <v>0.9673867990798275</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.5748171662461232</v>
+        <v>-0.7198329799829908</v>
       </c>
       <c r="C44">
-        <v>0.2224012842290186</v>
+        <v>0.651565346924698</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.8754273426016059</v>
+        <v>-1.657770297969345</v>
       </c>
       <c r="C45">
-        <v>-0.7394381554030078</v>
+        <v>-1.271769021585242</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.268676938634881</v>
+        <v>0.6759487598789916</v>
       </c>
       <c r="C46">
-        <v>-0.2369340886967985</v>
+        <v>0.8588291375508426</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.3683965929531888</v>
+        <v>0.5971058829760589</v>
       </c>
       <c r="C47">
-        <v>1.245681557080216</v>
+        <v>1.685056767291681</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.3544574006913463</v>
+        <v>-1.023607142391476</v>
       </c>
       <c r="C48">
-        <v>-0.5417269105577857</v>
+        <v>0.3831652117079455</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.6196878572545819</v>
+        <v>0.3873471051169634</v>
       </c>
       <c r="C49">
-        <v>0.0089204778195206</v>
+        <v>-0.03154472974583714</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.3692654519310435</v>
+        <v>1.939270988060602</v>
       </c>
       <c r="C50">
-        <v>-0.06670755260267947</v>
+        <v>2.424137411410246</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>-1.313686323124794</v>
+        <v>0.8081013725169113</v>
       </c>
       <c r="C51">
-        <v>1.778518504299431</v>
+        <v>0.3743984294836385</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.05969401378852379</v>
+      </c>
+      <c r="C52">
+        <v>1.004728052640949</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>-0.3250835767790191</v>
+      </c>
+      <c r="C53">
+        <v>0.2681096654996746</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>-0.1159879033104885</v>
+      </c>
+      <c r="C54">
+        <v>0.2518274460557789</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>-0.9937975860412931</v>
+      </c>
+      <c r="C55">
+        <v>0.7221492337560457</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0.7425552595237562</v>
+      </c>
+      <c r="C56">
+        <v>1.331043424633139</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>0.7006674486457899</v>
+      </c>
+      <c r="C57">
+        <v>1.402181336413832</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-1.396712975917322</v>
+      </c>
+      <c r="C58">
+        <v>-0.8078975159680077</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>1.821507415535939</v>
+      </c>
+      <c r="C59">
+        <v>-0.4585660827460971</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0.04488852281364469</v>
+      </c>
+      <c r="C60">
+        <v>-0.4197998498941427</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.3034429082301746</v>
+      </c>
+      <c r="C61">
+        <v>0.8009645739441337</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>-1.239019102989053</v>
+      </c>
+      <c r="C62">
+        <v>-1.591326442015991</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>-0.02992151644155043</v>
+      </c>
+      <c r="C63">
+        <v>-0.8739045163489002</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>0.02338316167825255</v>
+      </c>
+      <c r="C64">
+        <v>-0.8708073378492562</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.9178732652038806</v>
+      </c>
+      <c r="C65">
+        <v>-0.8506530971109609</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>0.2451527696667237</v>
+      </c>
+      <c r="C66">
+        <v>0.05189207880813637</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>-1.512268256836455</v>
+      </c>
+      <c r="C67">
+        <v>-0.1005188562323432</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>-0.8236334202708623</v>
+      </c>
+      <c r="C68">
+        <v>-1.064013240995925</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>-0.330211637621325</v>
+      </c>
+      <c r="C69">
+        <v>-0.5816114469355841</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.4709071291525093</v>
+      </c>
+      <c r="C70">
+        <v>0.8329260534009324</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-1.728060502595326</v>
+      </c>
+      <c r="C71">
+        <v>-2.076156474650044</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>1.236279521893247</v>
+      </c>
+      <c r="C72">
+        <v>-0.9121909367042758</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>-0.4588193282833801</v>
+      </c>
+      <c r="C73">
+        <v>0.402236158739229</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>1.421624525545018</v>
+      </c>
+      <c r="C74">
+        <v>-0.3624849084988526</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>-0.259296171993743</v>
+      </c>
+      <c r="C75">
+        <v>0.5502858209764492</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>-0.4277523049735731</v>
+      </c>
+      <c r="C76">
+        <v>0.8396190420336536</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-0.3560097915149929</v>
+      </c>
+      <c r="C77">
+        <v>0.2416637595574615</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>-0.6076808494773869</v>
+      </c>
+      <c r="C78">
+        <v>-0.6464366176751843</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>1.404847786839356</v>
+      </c>
+      <c r="C79">
+        <v>0.8634835022320446</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>-0.9526216437812826</v>
+      </c>
+      <c r="C80">
+        <v>-0.07555821141422092</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-0.05336281350311324</v>
+      </c>
+      <c r="C81">
+        <v>-1.320039408727531</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>0.7405257190850586</v>
+      </c>
+      <c r="C82">
+        <v>0.6368924520756445</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>0.4358716263302753</v>
+      </c>
+      <c r="C83">
+        <v>0.1208833850741018</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>2.308142400721469</v>
+      </c>
+      <c r="C84">
+        <v>1.028339242621741</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>-1.325968630796952</v>
+      </c>
+      <c r="C85">
+        <v>-0.4823771667995732</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>0.3046522533056323</v>
+      </c>
+      <c r="C86">
+        <v>-0.9526283254732903</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-0.5000842339742404</v>
+      </c>
+      <c r="C87">
+        <v>-0.2125041498924678</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>-1.12170183194951</v>
+      </c>
+      <c r="C88">
+        <v>-0.9791459362369648</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>0.2622905148913113</v>
+      </c>
+      <c r="C89">
+        <v>-0.8522367490635731</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>-0.114727450249153</v>
+      </c>
+      <c r="C90">
+        <v>1.329237495259822</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>-1.341865776229317</v>
+      </c>
+      <c r="C91">
+        <v>-0.9949429413159184</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>1.077652559535829</v>
+      </c>
+      <c r="C92">
+        <v>-1.036320331523553</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>1.734704867015151</v>
+      </c>
+      <c r="C93">
+        <v>-0.03671557126082214</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>-1.383969542133071</v>
+      </c>
+      <c r="C94">
+        <v>0.987678612147227</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>-1.24594878514439</v>
+      </c>
+      <c r="C95">
+        <v>-1.428757281334203</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>-0.2778364613274923</v>
+      </c>
+      <c r="C96">
+        <v>0.02234317723540075</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>0.600707465993818</v>
+      </c>
+      <c r="C97">
+        <v>0.005460496306641971</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-0.02111090065129219</v>
+      </c>
+      <c r="C98">
+        <v>-0.6213388029232426</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>1.526898931096692</v>
+      </c>
+      <c r="C99">
+        <v>1.797851586953601</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>1.080025196230076</v>
+      </c>
+      <c r="C100">
+        <v>0.6997641531746142</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>-0.4856518145909227</v>
+      </c>
+      <c r="C101">
+        <v>0.6778798508633672</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>0.4199740562554103</v>
+      </c>
+      <c r="C102">
+        <v>-0.08156865396829116</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>1.104744262533768</v>
+      </c>
+      <c r="C103">
+        <v>0.4555839816484896</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-1.0729729927941</v>
+      </c>
+      <c r="C104">
+        <v>1.141059195167081</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.1856801143466647</v>
+      </c>
+      <c r="C105">
+        <v>-0.487540085113415</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>1.156600723840591</v>
+      </c>
+      <c r="C106">
+        <v>0.4022935963661579</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.1784012644169858</v>
+      </c>
+      <c r="C107">
+        <v>0.2261906339921668</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>0.2511495888282594</v>
+      </c>
+      <c r="C108">
+        <v>1.558880720003139</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.6187435475913367</v>
+      </c>
+      <c r="C109">
+        <v>0.5111749049406072</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-0.3137823981792321</v>
+      </c>
+      <c r="C110">
+        <v>-0.08026436195936336</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.6771614438321552</v>
+      </c>
+      <c r="C111">
+        <v>0.4321855965564025</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.5004236403126598</v>
+      </c>
+      <c r="C112">
+        <v>1.372089483527678</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-2.455984165804322</v>
+      </c>
+      <c r="C113">
+        <v>-2.126390286988538</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-1.393674878256555</v>
+      </c>
+      <c r="C114">
+        <v>-0.650968039260467</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.4850006998420889</v>
+      </c>
+      <c r="C115">
+        <v>-0.6161550667358228</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-1.827810220358967</v>
+      </c>
+      <c r="C116">
+        <v>-1.591187233239399</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.5869024692550052</v>
+      </c>
+      <c r="C117">
+        <v>-1.131601715357583</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.6404467326553676</v>
+      </c>
+      <c r="C118">
+        <v>-1.259455372671968</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.1036307425927106</v>
+      </c>
+      <c r="C119">
+        <v>0.07604023528134726</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.4160942104678121</v>
+      </c>
+      <c r="C120">
+        <v>-0.4065219766188951</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.6485308240449643</v>
+      </c>
+      <c r="C121">
+        <v>0.05099277001945154</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.326159005418935</v>
+      </c>
+      <c r="C122">
+        <v>-0.4320749483172067</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>-0.2783055058721036</v>
+      </c>
+      <c r="C123">
+        <v>0.007150651964452859</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>2.187157680181364</v>
+      </c>
+      <c r="C124">
+        <v>0.3577230062871134</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>1.064326585280905</v>
+      </c>
+      <c r="C125">
+        <v>2.518855845632118</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.6456595088488597</v>
+      </c>
+      <c r="C126">
+        <v>-0.494501817981043</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-1.771295052228762</v>
+      </c>
+      <c r="C127">
+        <v>0.5142494099077967</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.2037810850269751</v>
+      </c>
+      <c r="C128">
+        <v>0.6951312514111014</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.4917770186353871</v>
+      </c>
+      <c r="C129">
+        <v>-0.5126199778279995</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.9908188787390463</v>
+      </c>
+      <c r="C130">
+        <v>-0.6746061014729505</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-0.009240746939517104</v>
+      </c>
+      <c r="C131">
+        <v>0.6429182478788229</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-0.7932481265914639</v>
+      </c>
+      <c r="C132">
+        <v>1.486178451766992</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.758381592375306</v>
+      </c>
+      <c r="C133">
+        <v>-0.0425700065839687</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-0.3187004671932214</v>
+      </c>
+      <c r="C134">
+        <v>-0.02504453741421089</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.0725152340444755</v>
+      </c>
+      <c r="C135">
+        <v>0.04196309095290071</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.740537596588656</v>
+      </c>
+      <c r="C136">
+        <v>-0.9529831103760482</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>0.3860243923184942</v>
+      </c>
+      <c r="C137">
+        <v>0.323421191518691</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.4453329540730713</v>
+      </c>
+      <c r="C138">
+        <v>1.430789767280319</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.9608167344268933</v>
+      </c>
+      <c r="C139">
+        <v>0.6886701998370339</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.4142088877855565</v>
+      </c>
+      <c r="C140">
+        <v>0.1128265294815299</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.1686421950187078</v>
+      </c>
+      <c r="C141">
+        <v>-0.8530980104953758</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>0.5865475821607989</v>
+      </c>
+      <c r="C142">
+        <v>0.1998222864857823</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>0.5646717318591022</v>
+      </c>
+      <c r="C143">
+        <v>-1.199991637195961</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.2845720536221629</v>
+      </c>
+      <c r="C144">
+        <v>-0.3708007985554634</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-1.758672629796908</v>
+      </c>
+      <c r="C145">
+        <v>-0.5182955414151182</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.5999883437178594</v>
+      </c>
+      <c r="C146">
+        <v>-1.308976917001779</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-2.670003359531855</v>
+      </c>
+      <c r="C147">
+        <v>0.9888354547106153</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.9507788267968008</v>
+      </c>
+      <c r="C148">
+        <v>-1.139731143224948</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-3.466387958646107</v>
+      </c>
+      <c r="C149">
+        <v>-2.335341613787037</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-0.06126354367695715</v>
+      </c>
+      <c r="C150">
+        <v>-0.3180082828107658</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.4717233732589651</v>
+      </c>
+      <c r="C151">
+        <v>-0.8457349763167988</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-2.619702590886626</v>
+      </c>
+      <c r="C152">
+        <v>-1.242746087435822</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>2.338555095668406</v>
+      </c>
+      <c r="C153">
+        <v>1.985695618027322</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-0.01665805414698546</v>
+      </c>
+      <c r="C154">
+        <v>1.197707302440413</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-1.067178199816213</v>
+      </c>
+      <c r="C155">
+        <v>-0.636452384407849</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>1.056831256311261</v>
+      </c>
+      <c r="C156">
+        <v>0.775713378325812</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>1.101494966967029</v>
+      </c>
+      <c r="C157">
+        <v>0.299251541612152</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.07723758167741288</v>
+      </c>
+      <c r="C158">
+        <v>0.477409978376112</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.1012131986408562</v>
+      </c>
+      <c r="C159">
+        <v>0.06278333047614637</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.6797467209115861</v>
+      </c>
+      <c r="C160">
+        <v>0.7081089515179618</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.03832728438516489</v>
+      </c>
+      <c r="C161">
+        <v>0.4298838953214895</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>1.906862575620539</v>
+      </c>
+      <c r="C162">
+        <v>0.09642405676675614</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.972826425352622</v>
+      </c>
+      <c r="C163">
+        <v>-0.6741067564046661</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>-0.5047370957195859</v>
+      </c>
+      <c r="C164">
+        <v>-0.05486979115805526</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-0.7132896990618528</v>
+      </c>
+      <c r="C165">
+        <v>-0.340264554971355</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-0.08655802994332627</v>
+      </c>
+      <c r="C166">
+        <v>-0.4299026369222438</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>0.1993060398467561</v>
+      </c>
+      <c r="C167">
+        <v>0.4785034312515042</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1.234239516370101</v>
+      </c>
+      <c r="C168">
+        <v>1.449411276833182</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-0.09128750514654674</v>
+      </c>
+      <c r="C169">
+        <v>-0.5658791838988414</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>0.7945151691520503</v>
+      </c>
+      <c r="C170">
+        <v>0.5780089211515048</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.2076505252934994</v>
+      </c>
+      <c r="C171">
+        <v>-1.008156603712814</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>1.199893915816981</v>
+      </c>
+      <c r="C172">
+        <v>0.5953415862685261</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>1.20734824495309</v>
+      </c>
+      <c r="C173">
+        <v>0.4837409625748625</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>-0.3010031356430724</v>
+      </c>
+      <c r="C174">
+        <v>0.05764257865814534</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-0.5448099386734335</v>
+      </c>
+      <c r="C175">
+        <v>0.9573992812795717</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-0.204529149386612</v>
+      </c>
+      <c r="C176">
+        <v>-0.5755581880335758</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-0.1520479599336654</v>
+      </c>
+      <c r="C177">
+        <v>-0.9269249990429396</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>1.156112097707345</v>
+      </c>
+      <c r="C178">
+        <v>0.9189750794365382</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>1.251598942817108</v>
+      </c>
+      <c r="C179">
+        <v>-0.008635589460487147</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.3922155931362368</v>
+      </c>
+      <c r="C180">
+        <v>-0.5243550815233755</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>-0.5781604179763821</v>
+      </c>
+      <c r="C181">
+        <v>-0.2357398112538223</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-0.6404208044810976</v>
+      </c>
+      <c r="C182">
+        <v>-0.5238297521721091</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-0.08930339554283995</v>
+      </c>
+      <c r="C183">
+        <v>-0.1129116052068352</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.286411874904853</v>
+      </c>
+      <c r="C184">
+        <v>-0.06484778761146978</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>1.008810426619708</v>
+      </c>
+      <c r="C185">
+        <v>0.316259427140702</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>0.3239731672357335</v>
+      </c>
+      <c r="C186">
+        <v>0.8506124314843776</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>0.003346730145937239</v>
+      </c>
+      <c r="C187">
+        <v>0.3597960292734844</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-1.74481716992216</v>
+      </c>
+      <c r="C188">
+        <v>-1.194308138985902</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>0.8273648909084858</v>
+      </c>
+      <c r="C189">
+        <v>1.704888352818796</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>1.695713252741249</v>
+      </c>
+      <c r="C190">
+        <v>1.664036474776128</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-1.172640001438091</v>
+      </c>
+      <c r="C191">
+        <v>-0.0480591821657807</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.1670444282853149</v>
+      </c>
+      <c r="C192">
+        <v>-0.07890338374823086</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>0.986540786732326</v>
+      </c>
+      <c r="C193">
+        <v>1.257473505554342</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.1164367652342121</v>
+      </c>
+      <c r="C194">
+        <v>-0.9421510178081245</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.05569922012912375</v>
+      </c>
+      <c r="C195">
+        <v>-0.1741969114348688</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>-2.148128573140418</v>
+      </c>
+      <c r="C196">
+        <v>0.5673508183076612</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0.1068420268462941</v>
+      </c>
+      <c r="C197">
+        <v>1.189809681774449</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.7633847822673537</v>
+      </c>
+      <c r="C198">
+        <v>1.260259900360795</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>-1.209010974700745</v>
+      </c>
+      <c r="C199">
+        <v>0.5652089724254148</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-1.351703255786168</v>
+      </c>
+      <c r="C200">
+        <v>-0.9747680670500781</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-0.4658989963031812</v>
+      </c>
+      <c r="C201">
+        <v>1.444823756134868</v>
       </c>
     </row>
   </sheetData>
